--- a/data/excel/petroleo_mensual.xlsx
+++ b/data/excel/petroleo_mensual.xlsx
@@ -13083,7 +13083,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21T18:44:48Z</t>
+          <t>2026-10-22T13:57:24Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/petroleo_mensual.xlsx
+++ b/data/excel/petroleo_mensual.xlsx
@@ -13083,7 +13083,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22T13:57:24Z</t>
+          <t>2026-10-23T17:51:24Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/petroleo_mensual.xlsx
+++ b/data/excel/petroleo_mensual.xlsx
@@ -13083,7 +13083,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23T17:51:24Z</t>
+          <t>2026-10-26T13:22:32Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/petroleo_mensual.xlsx
+++ b/data/excel/petroleo_mensual.xlsx
@@ -13083,7 +13083,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26T13:22:32Z</t>
+          <t>2026-10-27T13:03:34Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/petroleo_mensual.xlsx
+++ b/data/excel/petroleo_mensual.xlsx
@@ -13083,7 +13083,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27T13:03:34Z</t>
+          <t>2026-10-28T18:48:49Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/petroleo_mensual.xlsx
+++ b/data/excel/petroleo_mensual.xlsx
@@ -13083,7 +13083,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28T18:48:49Z</t>
+          <t>2026-10-29T18:55:54Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/petroleo_mensual.xlsx
+++ b/data/excel/petroleo_mensual.xlsx
@@ -13083,7 +13083,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29T18:55:54Z</t>
+          <t>2026-10-30T18:03:55Z</t>
         </is>
       </c>
     </row>
